--- a/action_cop/output_excels/12_Event_Calendar.xlsx
+++ b/action_cop/output_excels/12_Event_Calendar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F110"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2891,76 +2891,76 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HCL Technologies Limited</t>
+          <t>Avenue Supermarts Limited</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>To consider and approve the financial results for the period ended September 30, 2026 and dividend</t>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>12-Oct-2026</t>
+          <t>10-Oct-2026</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ICICI Prudential Life Insurance Company Limited</t>
+          <t>HCL Technologies Limited</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>To consider and approve the unaudited standalone financial statements and financial results of the Company for the quarter and half year ended September 30, 2026.</t>
+          <t>To consider and approve the financial results for the period ended September 30, 2026 and dividend</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>13-Oct-2026</t>
+          <t>12-Oct-2026</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Bharat Heavy Electricals Limited</t>
+          <t>RBL Bank Limited</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2970,61 +2970,61 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Board Meeting for Unaudited Financial Results for &amp; upto the quarter ended30th September, 2026 and Closure of Trading Window thereof</t>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>14-Oct-2026</t>
+          <t>12-Oct-2026</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ICICI Lombard General Insurance Company Limited</t>
+          <t>Sun Pharmaceutical Industries Limited</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Other business matters</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>To consider and approve the financial results for the period ended September 30, 2026 and declaration of interim dividend, if any</t>
+          <t>Board meeting intimation for consideration and approval of the issuance of listed, rated, unsecured, redeemable, non-convertible debentures</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>14-Oct-2026</t>
+          <t>12-Oct-2026</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Angel One Limited</t>
+          <t>ICICI Prudential Life Insurance Company Limited</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3034,29 +3034,29 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
+          <t>To consider and approve the unaudited standalone financial statements and financial results of the Company for the quarter and half year ended September 30, 2026.</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HDFC Asset Management Company Limited</t>
+          <t>Tata Elxsi Limited</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3071,98 +3071,98 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>13-Oct-2026</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Limited</t>
+          <t>Bharat Heavy Electricals Limited</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Financial Results/Fund Raising</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>To consider and approve the financial results for the period ended September 30, 2026 and Fund Raising</t>
+          <t>Board Meeting for Unaudited Financial Results for &amp; upto the quarter ended30th September, 2026 and Closure of Trading Window thereof</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nestle India Limited</t>
+          <t>ICICI Lombard General Insurance Company Limited</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>To consider and approve the unaudited financial results (standalone and consolidated) for the second quarter and half year ending September 30, 2026</t>
+          <t>To consider and approve the financial results for the period ended September 30, 2026 and declaration of interim dividend, if any</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>14-Oct-2026</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tech Mahindra Limited</t>
+          <t>360 ONE WAM LIMITED</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend/Bonus/Other business matters</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>To consider and approve the financial results for the period ended September 30, 2026, dividend, bonus and other business matters</t>
+          <t>To consider and approve the financial results for the period ended September 30, 2026 and second interim dividend for FY 2026-27</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3172,19 +3172,19 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Axis Bank Limited</t>
+          <t>Angel One Limited</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3199,56 +3199,56 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>17-Oct-2026</t>
+          <t>15-Oct-2026</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HDFC Bank Limited</t>
+          <t>Angel One Limited</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>To consider and approve the unaudited standalone and consolidated financial results of the Bank for the quarter/half-year ending September 30, 2026</t>
+          <t>Intimation of Board Meeting for Declaration of Interim Dividend and Record date pursuant to Regulation 29 and 42 of SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 ("Listing Regulations").</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>17-Oct-2026</t>
+          <t>15-Oct-2026</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ICICI Bank Limited</t>
+          <t>HDFC Asset Management Company Limited</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3258,93 +3258,93 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>To inter alia consider and approve the unaudited financial results (standalone and consolidated) for the quarter and six months ending September 30, 2026.</t>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>17-Oct-2026</t>
+          <t>15-Oct-2026</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>UltraTech Cement Limited</t>
+          <t>HDFC Life Insurance Company Limited</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Fund Raising</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
+          <t>To consider and approve the financial results for the period ended September 30, 2026 and Fund Raising</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>19-Oct-2026</t>
+          <t>15-Oct-2026</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Adani Power Limited</t>
+          <t>Indian Railway Finance Corporation Limited</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
+          <t>To consider and approve the financial results for the period ended September 30, 2026 and dividend</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>15-Oct-2026</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Coforge Limited</t>
+          <t>Jio Financial Services Limited</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3354,29 +3354,29 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
+          <t>To consider and approve the unaudited financial results for the quarter and half year ended September 30, 2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>15-Oct-2026</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>LTF</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Limited</t>
+          <t>L&amp;T Finance Limited</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3391,24 +3391,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>15-Oct-2026</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IndusInd Bank Limited</t>
+          <t>Nestle India Limited</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3418,61 +3418,61 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>To consider and approve the Unaudited Standalone and Consolidated Financial Results for the quarter and half-year ending September 30, 2026</t>
+          <t>To consider and approve the unaudited financial results (standalone and consolidated) for the second quarter and half year ending September 30, 2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>15-Oct-2026</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Infosys Limited</t>
+          <t>Persistent Systems Limited</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results/Other business matters</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>To consider and approve the financial results for the period ended September 30, 2026 and dividend</t>
+          <t>To consider and approve the financial results for the period ended September 30, 2026 and other business matters</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>15-Oct-2026</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>JSW Steel Limited</t>
+          <t>Polycab India Limited</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3487,56 +3487,56 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>15-Oct-2026</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SHREE CEMENT LIMITED</t>
+          <t>Tech Mahindra Limited</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Financial Results</t>
+          <t>Financial Results/Dividend/Bonus/Other business matters</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
+          <t>To consider and approve the financial results for the period ended September 30, 2026, dividend, bonus and other business matters</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>23-Oct-2026</t>
+          <t>15-Oct-2026</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IDFC First Bank Limited</t>
+          <t>Wipro Limited</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3546,29 +3546,29 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>To consider and approve the financial results for the quarter and half year ended September 30, 2026</t>
+          <t>Pursuant to Regulation 29(1) of the SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015, it is hereby informed that the next meeting of the Board of Directors of Wipro Limited ( the Company ) will be held over October 14-15, 2026 to consider and approve, inter alia:a) the condensed audited standalone and consolidated financial results of the Company under lndAS for the quarter and half year ended September 30, 2026.b) the condensed audited consolidated financial results of the Company under IFRS for the quarter and half year ended September 30, 2026.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>24-Oct-2026</t>
+          <t>15-Oct-2026</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>CROMPTON</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Kfin Technologies Limited</t>
+          <t>Crompton Greaves Consumer Electricals Limited</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3578,29 +3578,29 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>To consider and approve the standalone and consolidated unaudited financial results of the Company for the quarter and half year ending September 30, 2026.</t>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>26-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cipla Limited</t>
+          <t>The Federal Bank  Limited</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3610,29 +3610,29 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Cipla limited has informed the Exchange about Board Meeting to be held on 27th October, 2026 to inter-alia consider and approve the Unaudited Financial results of the Company for the quarter and half-year ended 30th September, 2026.</t>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>27-Oct-2026</t>
+          <t>16-Oct-2026</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Max Financial Services Limited</t>
+          <t>Axis Bank Limited</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3647,24 +3647,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>27-Oct-2026</t>
+          <t>17-Oct-2026</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Blue Star Limited</t>
+          <t>HDFC Bank Limited</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3674,61 +3674,61 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
+          <t>To consider and approve the unaudited standalone and consolidated financial results of the Bank for the quarter/half-year ending September 30, 2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>17-Oct-2026</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Computer Age Management Services Limited</t>
+          <t>ICICI Bank Limited</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>To consider and approve the unaudited financial results for the period ended September 30, 2026 and dividend</t>
+          <t>To inter alia consider and approve the unaudited financial results (standalone and consolidated) for the quarter and six months ending September 30, 2026.</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>29-Oct-2026</t>
+          <t>17-Oct-2026</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>YESBANK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cummins India Limited</t>
+          <t>Yes Bank Limited</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3738,93 +3738,93 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>To consider and approve the financial results for the quarter and half year ending September 30, 2026</t>
+          <t>Intimation of the date of the Board Meeting for considering Un-audited Financial Results for the Quarter (Q2) and Half Year ended September 30, 2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>04-Nov-2026</t>
+          <t>17-Oct-2026</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Dabur India Limited</t>
+          <t>Bajaj Finance Limited</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Financial Results/Dividend</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>To consider and approve the unaudited financial results for the quarter and half year ending on September 30, 2026 and Interim dividend for the Financial Year 2026-27</t>
+          <t>To consider and approve the unaudited standalone and consolidated financial results for the quarter and half year ended September 30, 2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>04-Nov-2026</t>
+          <t>19-Oct-2026</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Limited</t>
+          <t>UltraTech Cement Limited</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>To consider and approve the financial results for the period ended September 30, 2026 and other business matters</t>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>05-Nov-2026</t>
+          <t>19-Oct-2026</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MphasiS Limited</t>
+          <t>Adani Energy Solutions Limited</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3834,61 +3834,61 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
+          <t>To consider and approve the Unaudited financial results for the period ended September 30, 2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>05-Nov-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Bosch Limited</t>
+          <t>Swiggy Limited</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Financial Results/Other business matters</t>
+          <t>Financial Results</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>To consider and approve the financial results for the period ended September 30, 2026 and other business matters</t>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>06-Nov-2026</t>
+          <t>22-Oct-2026</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Hindalco Industries Limited</t>
+          <t>Adani Power Limited</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3898,49 +3898,1201 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>To consider and approve the Unaudited Standalone and Consolidated financial results of the Company for the quarter ending September 30, 2026</t>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>06-Nov-2026</t>
+          <t>23-Oct-2026</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-10-01 10:50:17</t>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Coforge Limited</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>23-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Dr. Reddy's Laboratories Limited</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>23-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Godrej Properties Limited</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>To consider and approve the unaudited financial results for the quarter and half year ended September 30, 2026.</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>23-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>IndusInd Bank Limited</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>To consider and approve the Unaudited Standalone and Consolidated Financial Results for the quarter and half-year ending September 30, 2026</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>23-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Infosys Limited</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>To consider and approve the financial results for the period ended September 30, 2026 and dividend</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>23-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>JINDAL STEEL LIMITED</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>23-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>JSW Steel Limited</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>23-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SHREE CEMENT LIMITED</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>23-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Torrent Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Other business matters</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>To consider other business matters</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>23-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Torrent Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>the Audited Financial Results on Standalone basis and Unaudited Financial Results (with limited review) on Consolidated basis of the Company for the quarter and half year ended on 30-Sep-26.</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>23-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>IDFC First Bank Limited</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>To consider and approve the financial results for the quarter and half year ended September 30, 2026</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>24-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Kotak Mahindra Bank Limited</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>To consider and approve the Standalone and Consolidated Unaudited Financial Results for the quarter and half year ended September 30, 2026</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>24-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Kfin Technologies Limited</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>To consider and approve the standalone and consolidated unaudited financial results of the Company for the quarter and half year ending September 30, 2026.</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>26-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Sona BLW Precision Forgings Limited</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>26-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Bajaj Auto Limited</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>27-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Cipla Limited</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Cipla limited has informed the Exchange about Board Meeting to be held on 27th October, 2026 to inter-alia consider and approve the Unaudited Financial results of the Company for the quarter and half-year ended 30th September, 2026.</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>27-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Indus Towers Limited</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>To consider and approve the Audited Financial Results (Standalone &amp; Consolidated) for the second quarter (Q2) and half year ended on September 30, 2026.</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>27-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Maruti Suzuki India Limited</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>27-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Max Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>27-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Radico Khaitan Limited</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>27-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Adani Ports and Special Economic Zone Limited</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>28-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Hindustan Unilever Limited</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Board Meeting Intimation for Consideration of Unaudited Standalone and Consolidated Financial Results for quarter and half year ended 30th September, 2026 and payment of Interim Dividend (if any)</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>28-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Asian Paints Limited</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>This is to inform you that a meeting of the Board of Directors of the Company will be held on Thursday, 29th October 2026, inter alia, to consider the following:1.Approval of audited standalone financial results of the Company for the quarter and half-year ended 30th September 2026; 2.Approval of unaudited consolidated financial results of the Company for the quarter and half-year ended 30th September 2026; and 3.Declaration of interim dividend, if any, for the financial year ending 31st March 2027. It is further informed that the record date for payment of interim dividend, if declared, will be Wednesday, 4th November 2026.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>BLUESTARCO</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Blue Star Limited</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Computer Age Management Services Limited</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>To consider and approve the unaudited financial results for the period ended September 30, 2026 and dividend</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Godrej Consumer Products Limited</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>To consider and approve the financial results for the period ended September 30, 2026 and dividend</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Trent Limited</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Notice of Board Meeting</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>29-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Bajaj Finserv Limited</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>To consider and approve the unaudited standalone and consolidated financial results for the quarter and half year ended 30 September 2026.</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>03-Nov-2026</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Bajaj Holdings &amp; Investment Limited</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>To consider and approve the unaudited standalone &amp; consolidated financial results for the quarter and half year ended 30 September 2026</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>03-Nov-2026</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Cummins India Limited</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>To consider and approve the financial results for the quarter and half year ending September 30, 2026</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>04-Nov-2026</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Dabur India Limited</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Financial Results/Dividend</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>To consider and approve the unaudited financial results for the quarter and half year ending on September 30, 2026 and Interim dividend for the Financial Year 2026-27</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>04-Nov-2026</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Mahindra &amp; Mahindra Limited</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>To consider and approve the financial results for the period ended September 30, 2026 and other business matters</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>05-Nov-2026</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>MphasiS Limited</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>To consider and approve the financial results for the period ended September 30, 2026</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>05-Nov-2026</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Bosch Limited</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>To consider and approve the financial results for the period ended September 30, 2026 and other business matters</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>06-Nov-2026</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Hindalco Industries Limited</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>To consider and approve the Unaudited Standalone and Consolidated financial results of the Company for the quarter ending September 30, 2026</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>06-Nov-2026</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Tata Power Company Limited</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Financial Results/Other business matters</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>To consider and approve the financial results for the quarter and half year ended September 30, 2026, and other business matters</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>11-Nov-2026</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
           <t>ABB</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>ABB India Limited</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Financial Results</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Financial Results</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
         <is>
           <t>To consider and approve the financial results for the period ended September 30, 2026</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="E146" t="inlineStr">
         <is>
           <t>13-Nov-2026</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-10-01 10:50:17</t>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:16:03</t>
         </is>
       </c>
     </row>
